--- a/task/关键标准答案.xlsx
+++ b/task/关键标准答案.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="R6a22ae7368184f86"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="Rc9fc6374b766412e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="Rffefd0a8ed4a47f6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="R757747381f4b4168"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="R1757b7dd2f354e78"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="Rbcc446943cea483d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="R7b455aa9f7574989"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="R42808818150f4f6d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="R730fb9d211944399"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="R0a79097603554c6c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -394,31 +394,17 @@
       </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
-      <x:c r="A8" s="5" t="str">
+      <x:c r="A8" s="6" t="str">
         <x:v>租约事件报告</x:v>
       </x:c>
-      <x:c r="B8" s="5" t="str">
+      <x:c r="B8" s="6" t="str">
         <x:v>reports/lease_events.csv</x:v>
       </x:c>
-      <x:c r="C8" s="5" t="str">
+      <x:c r="C8" s="6" t="str">
         <x:v>汇总发布租约和申请校验事件</x:v>
       </x:c>
-      <x:c r="D8" s="5" t="str">
-        <x:v>与runtime_events中的JSON逐项一致</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="15" hidden="0" customHeight="1">
-      <x:c r="A9" s="6" t="str">
-        <x:v>运行事件</x:v>
-      </x:c>
-      <x:c r="B9" s="6" t="str">
-        <x:v>runtime_events/*/*.json</x:v>
-      </x:c>
-      <x:c r="C9" s="6" t="str">
-        <x:v>保留两个场景的本次业务事件</x:v>
-      </x:c>
-      <x:c r="D9" s="6" t="str">
-        <x:v>每个文件可解析且主键不重复</x:v>
+      <x:c r="D8" s="6" t="str">
+        <x:v>与本次Airflow任务日志及场景结果一致</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -924,30 +910,16 @@
       </x:c>
     </x:row>
     <x:row r="5" ht="15" hidden="0" customHeight="1">
-      <x:c r="A5" s="5" t="str">
-        <x:v>运行事件</x:v>
-      </x:c>
-      <x:c r="B5" s="5" t="str">
-        <x:v>JSON键顺序和空白可以变化</x:v>
-      </x:c>
-      <x:c r="C5" s="5" t="str">
-        <x:v>scenario_id、event_order、event_type、object_id和detail不能变化</x:v>
-      </x:c>
-      <x:c r="D5" s="5" t="str">
-        <x:v>解析JSON后按业务主键比较</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="15" hidden="0" customHeight="1">
-      <x:c r="A6" s="6" t="str">
+      <x:c r="A5" s="6" t="str">
         <x:v>失败日志</x:v>
       </x:c>
-      <x:c r="B6" s="6" t="str">
+      <x:c r="B5" s="6" t="str">
         <x:v>堆栈路径和日志时间可以变化</x:v>
       </x:c>
-      <x:c r="C6" s="6" t="str">
+      <x:c r="C5" s="6" t="str">
         <x:v>校验中止的失败对象、后续阻断、租约释放和DagRun失败不能变化</x:v>
       </x:c>
-      <x:c r="D6" s="6" t="str">
+      <x:c r="D5" s="6" t="str">
         <x:v>结合DagRun、TaskInstance和事件报告判断</x:v>
       </x:c>
     </x:row>

--- a/task/关键标准答案.xlsx
+++ b/task/关键标准答案.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="Rbcc446943cea483d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="R7b455aa9f7574989"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="R42808818150f4f6d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="R730fb9d211944399"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="R0a79097603554c6c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="R091aca974682486b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="R9f2d9dad963049dc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="Ra463ce9973e74ddc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="R71a9d3f1457f4c60"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="R853bda0e743f4bae"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -497,96 +497,152 @@
         <x:v>dag_contract.csv</x:v>
       </x:c>
       <x:c r="B6" s="5" t="str">
-        <x:v>acquire_release_lease.is_setup</x:v>
+        <x:v>release_release_lease.trigger_rule</x:v>
       </x:c>
       <x:c r="C6" s="5" t="str">
-        <x:v>true</x:v>
+        <x:v>all_done_setup_success</x:v>
       </x:c>
       <x:c r="D6" s="5" t="str">
-        <x:v>最终DagBag任务对象</x:v>
+        <x:v>release_policy.json的teardown_trigger_rule</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
       <x:c r="A7" s="5" t="str">
-        <x:v>dag_contract.csv</x:v>
+        <x:v>lease_events.csv</x:v>
       </x:c>
       <x:c r="B7" s="5" t="str">
-        <x:v>release_release_lease.is_teardown</x:v>
+        <x:v>LEASE_ACQUIRED.event_order</x:v>
       </x:c>
       <x:c r="C7" s="5" t="str">
-        <x:v>true</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D7" s="5" t="str">
-        <x:v>最终DagBag任务对象</x:v>
+        <x:v>release_policy.json的lease_acquired_order</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
       <x:c r="A8" s="5" t="str">
-        <x:v>dag_contract.csv</x:v>
+        <x:v>lease_events.csv</x:v>
       </x:c>
       <x:c r="B8" s="5" t="str">
-        <x:v>release_release_lease.trigger_rule</x:v>
+        <x:v>LEASE_RELEASED.event_order</x:v>
       </x:c>
       <x:c r="C8" s="5" t="str">
-        <x:v>all_done_setup_success</x:v>
+        <x:v>999</x:v>
       </x:c>
       <x:c r="D8" s="5" t="str">
-        <x:v>Airflow teardown任务对象</x:v>
+        <x:v>release_policy.json的lease_released_order</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
       <x:c r="A9" s="5" t="str">
-        <x:v>run_outcomes.csv</x:v>
+        <x:v>lease_events.csv</x:v>
       </x:c>
       <x:c r="B9" s="5" t="str">
-        <x:v>release_ready.observed_dag_state</x:v>
+        <x:v>LEASE_ACQUIRED.detail</x:v>
       </x:c>
       <x:c r="C9" s="5" t="str">
-        <x:v>success</x:v>
+        <x:v>release window opened</x:v>
       </x:c>
       <x:c r="D9" s="5" t="str">
-        <x:v>逻辑日期2026-08-11的DagRun</x:v>
+        <x:v>release_policy.json的lease_acquired_detail</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="15" hidden="0" customHeight="1">
       <x:c r="A10" s="5" t="str">
-        <x:v>run_outcomes.csv</x:v>
+        <x:v>lease_events.csv</x:v>
       </x:c>
       <x:c r="B10" s="5" t="str">
-        <x:v>verification_stop.observed_dag_state</x:v>
+        <x:v>LEASE_RELEASED.detail</x:v>
       </x:c>
       <x:c r="C10" s="5" t="str">
-        <x:v>failed</x:v>
+        <x:v>release window closed</x:v>
       </x:c>
       <x:c r="D10" s="5" t="str">
-        <x:v>逻辑日期2026-08-12的DagRun</x:v>
+        <x:v>release_policy.json的lease_released_detail</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="15" hidden="0" customHeight="1">
       <x:c r="A11" s="5" t="str">
+        <x:v>dag_contract.csv</x:v>
+      </x:c>
+      <x:c r="B11" s="5" t="str">
+        <x:v>acquire_release_lease.is_setup</x:v>
+      </x:c>
+      <x:c r="C11" s="5" t="str">
+        <x:v>true</x:v>
+      </x:c>
+      <x:c r="D11" s="5" t="str">
+        <x:v>最终DagBag任务对象</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
+      <x:c r="A12" s="5" t="str">
+        <x:v>dag_contract.csv</x:v>
+      </x:c>
+      <x:c r="B12" s="5" t="str">
+        <x:v>release_release_lease.is_teardown</x:v>
+      </x:c>
+      <x:c r="C12" s="5" t="str">
+        <x:v>true</x:v>
+      </x:c>
+      <x:c r="D12" s="5" t="str">
+        <x:v>最终DagBag任务对象</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="15" hidden="0" customHeight="1">
+      <x:c r="A13" s="5" t="str">
+        <x:v>run_outcomes.csv</x:v>
+      </x:c>
+      <x:c r="B13" s="5" t="str">
+        <x:v>release_ready.observed_dag_state</x:v>
+      </x:c>
+      <x:c r="C13" s="5" t="str">
+        <x:v>success</x:v>
+      </x:c>
+      <x:c r="D13" s="5" t="str">
+        <x:v>逻辑日期2026-08-11的DagRun</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="15" hidden="0" customHeight="1">
+      <x:c r="A14" s="5" t="str">
+        <x:v>run_outcomes.csv</x:v>
+      </x:c>
+      <x:c r="B14" s="5" t="str">
+        <x:v>verification_stop.observed_dag_state</x:v>
+      </x:c>
+      <x:c r="C14" s="5" t="str">
+        <x:v>failed</x:v>
+      </x:c>
+      <x:c r="D14" s="5" t="str">
+        <x:v>逻辑日期2026-08-12的DagRun</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="15" hidden="0" customHeight="1">
+      <x:c r="A15" s="5" t="str">
         <x:v>task_instance_evidence.csv</x:v>
       </x:c>
-      <x:c r="B11" s="5" t="str">
+      <x:c r="B15" s="5" t="str">
         <x:v>verification_stop.request_req_2404.verify.state</x:v>
       </x:c>
-      <x:c r="C11" s="5" t="str">
+      <x:c r="C15" s="5" t="str">
         <x:v>failed</x:v>
       </x:c>
-      <x:c r="D11" s="5" t="str">
+      <x:c r="D15" s="5" t="str">
         <x:v>失败对象来自rehearsal_scenarios.csv</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="15" hidden="0" customHeight="1">
-      <x:c r="A12" s="6" t="str">
+    <x:row r="16" ht="15" hidden="0" customHeight="1">
+      <x:c r="A16" s="6" t="str">
         <x:v>task_instance_evidence.csv</x:v>
       </x:c>
-      <x:c r="B12" s="6" t="str">
+      <x:c r="B16" s="6" t="str">
         <x:v>verification_stop.request_req_2405.verify.state</x:v>
       </x:c>
-      <x:c r="C12" s="6" t="str">
+      <x:c r="C16" s="6" t="str">
         <x:v>upstream_failed</x:v>
       </x:c>
-      <x:c r="D12" s="6" t="str">
+      <x:c r="D16" s="6" t="str">
         <x:v>REQ-2404失败后的顺序依赖</x:v>
       </x:c>
     </x:row>
